--- a/SomewhatEnhancedDisplay/package/LangMod/JP/SourceSheet.xlsx
+++ b/SomewhatEnhancedDisplay/package/LangMod/JP/SourceSheet.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="503">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -1555,6 +1555,12 @@
   </si>
   <si>
     <t xml:space="preserve">Displays HP- and MP-based durability in different colors on the health bars of characters with Mana Body.</t>
+  </si>
+  <si>
+    <t>Display Unidentified Items as Identified</t>
+  </si>
+  <si>
+    <t>Displays the same information for unidentified items as for identified items.</t>
   </si>
 </sst>
 </file>
@@ -2735,7 +2741,9 @@
       <c r="C68" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="D68" s="7"/>
+      <c r="D68" s="7" t="s">
+        <v>499</v>
+      </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="6" t="s">
@@ -3913,6 +3921,9 @@
       </c>
       <c r="C169" s="11" t="s">
         <v>486</v>
+      </c>
+      <c r="D169" s="11" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="170">

--- a/SomewhatEnhancedDisplay/package/LangMod/JP/SourceSheet.xlsx
+++ b/SomewhatEnhancedDisplay/package/LangMod/JP/SourceSheet.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="509">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -1561,6 +1561,24 @@
   </si>
   <si>
     <t>Displays the same information for unidentified items as for identified items.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mc_sed_reverseManaBodyHealthBar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">マナの体のHP/MP表示順を反転</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reverse Mana Body HP / MP Order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mc_sed_tooltipReverseManaBodyHealthBar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">マナの体を分割表示する体力バーのHPとMPの表示順を反転し、左からMP、HPの順で表示します。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reverses the HP / MP order on split Mana Body health bars, displaying MP on the left and HP on the right.</t>
   </si>
 </sst>
 </file>
@@ -3974,8 +3992,30 @@
         <v>498</v>
       </c>
     </row>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1">
+      <c r="A174" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="B174"/>
+      <c r="C174" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="D174" s="6" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="175" ht="15.75" customHeight="1">
+      <c r="A175" s="8" t="s">
+        <v>504</v>
+      </c>
+      <c r="B175"/>
+      <c r="C175" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>506</v>
+      </c>
+    </row>
     <row r="176" ht="15.75" customHeight="1"/>
     <row r="177" ht="15.75" customHeight="1"/>
     <row r="178" ht="15.75" customHeight="1"/>
